--- a/attacks-table.xlsx
+++ b/attacks-table.xlsx
@@ -1684,7 +1684,7 @@
           <t>UE modem</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Stateful + BaseBridge + LLFuzz + FirmState</t>
         </is>
@@ -2128,20 +2128,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2634,7 +2635,7 @@
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>Mintlify base URL used for Attack-name links: https://5g-security-docs.mintlify.app</t>
+          <t>Mintlify base URL used for Attack-name links: https://mobisense-94a32a34.mintlify.app</t>
         </is>
       </c>
     </row>
